--- a/data/group_home/data.xlsx
+++ b/data/group_home/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -577,19 +577,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="str">
-        <v>34.30722639</v>
+        <v>34.28434611</v>
       </c>
       <c r="C5" t="str">
-        <v>133.99956528</v>
+        <v>134.01455361</v>
       </c>
       <c r="D5" t="str">
-        <v>グループホーム　オアシス香西</v>
+        <v>グループホーム春風荘</v>
       </c>
       <c r="E5" t="str">
-        <v>高松市檀紙町1452-1</v>
+        <v>高松市円座町1300-2</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -621,19 +621,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="str">
-        <v>34.28434611</v>
+        <v>34.26092639</v>
       </c>
       <c r="C6" t="str">
-        <v>134.01455361</v>
+        <v>134.01459611</v>
       </c>
       <c r="D6" t="str">
-        <v>グループホーム春風荘</v>
+        <v>グループホームあい</v>
       </c>
       <c r="E6" t="str">
-        <v>高松市円座町1300-2</v>
+        <v>高松市川部町1300-1</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -665,19 +665,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="str">
-        <v>34.26092639</v>
+        <v>34.31523417</v>
       </c>
       <c r="C7" t="str">
-        <v>134.01459611</v>
+        <v>134.02003833</v>
       </c>
       <c r="D7" t="str">
-        <v>グループホームあい</v>
+        <v>西春日グループホーム</v>
       </c>
       <c r="E7" t="str">
-        <v>高松市川部町1300-1</v>
+        <v>高松市西春日町1511-1</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -709,19 +709,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="str">
-        <v>34.31523417</v>
+        <v>34.31362611</v>
       </c>
       <c r="C8" t="str">
-        <v>134.02003833</v>
+        <v>134.02590722</v>
       </c>
       <c r="D8" t="str">
-        <v>西春日グループホーム</v>
+        <v>グループホーム　ほおずき</v>
       </c>
       <c r="E8" t="str">
-        <v>高松市西春日町1511-1</v>
+        <v>高松市松並町649-1</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -753,19 +753,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="str">
-        <v>34.31362611</v>
+        <v>34.322645</v>
       </c>
       <c r="C9" t="str">
-        <v>134.02590722</v>
+        <v>134.04190278</v>
       </c>
       <c r="D9" t="str">
-        <v>グループホーム　ほおずき</v>
+        <v>グループホーム　暖暖</v>
       </c>
       <c r="E9" t="str">
-        <v>高松市松並町649-1</v>
+        <v>高松市室新町1-8</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -797,19 +797,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="str">
-        <v>34.322645</v>
+        <v>34.32076472</v>
       </c>
       <c r="C10" t="str">
-        <v>134.04190278</v>
+        <v>134.05430722</v>
       </c>
       <c r="D10" t="str">
-        <v>グループホーム　暖暖</v>
+        <v>グループホームすずらん</v>
       </c>
       <c r="E10" t="str">
-        <v>高松市室新町1-8</v>
+        <v>高松市伏石町2008-5</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -841,19 +841,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="str">
-        <v>34.32076472</v>
+        <v>34.30706611</v>
       </c>
       <c r="C11" t="str">
-        <v>134.05430722</v>
+        <v>134.04354472</v>
       </c>
       <c r="D11" t="str">
-        <v>グループホームすずらん</v>
+        <v>グループホーム　こすもす</v>
       </c>
       <c r="E11" t="str">
-        <v>高松市伏石町2008-5</v>
+        <v>高松市太田下町1868-2</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -885,19 +885,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="str">
-        <v>34.30706611</v>
+        <v>34.30438028</v>
       </c>
       <c r="C12" t="str">
-        <v>134.04354472</v>
+        <v>134.03901194</v>
       </c>
       <c r="D12" t="str">
-        <v>グループホーム　こすもす</v>
+        <v>グループホーム　花もめん</v>
       </c>
       <c r="E12" t="str">
-        <v>高松市太田下町1868-2</v>
+        <v>高松市太田下町2020-1</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -929,19 +929,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="str">
-        <v>34.30438028</v>
+        <v>34.30271583</v>
       </c>
       <c r="C13" t="str">
-        <v>134.03901194</v>
+        <v>134.01248361</v>
       </c>
       <c r="D13" t="str">
-        <v>グループホーム　花もめん</v>
+        <v>愛の家グループホーム高松成合</v>
       </c>
       <c r="E13" t="str">
-        <v>高松市太田下町2020-1</v>
+        <v>高松市成合町581</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -973,19 +973,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="str">
-        <v>34.30271583</v>
+        <v>34.29199222</v>
       </c>
       <c r="C14" t="str">
-        <v>134.01248361</v>
+        <v>134.02054167</v>
       </c>
       <c r="D14" t="str">
-        <v>愛の家グループホーム高松成合</v>
+        <v>らく楽一宮</v>
       </c>
       <c r="E14" t="str">
-        <v>高松市成合町581</v>
+        <v>高松市一宮町1568-1</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -1017,19 +1017,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="str">
-        <v>34.29199222</v>
+        <v>34.32359278</v>
       </c>
       <c r="C15" t="str">
-        <v>134.02054167</v>
+        <v>134.078855</v>
       </c>
       <c r="D15" t="str">
-        <v>らく楽一宮</v>
+        <v>グループホーム  木太</v>
       </c>
       <c r="E15" t="str">
-        <v>高松市一宮町1568-1</v>
+        <v>高松市木太町3749-3</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -1061,19 +1061,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="str">
-        <v>34.32359278</v>
+        <v>34.33139778</v>
       </c>
       <c r="C16" t="str">
-        <v>134.078855</v>
+        <v>134.09350611</v>
       </c>
       <c r="D16" t="str">
-        <v>グループホーム  木太</v>
+        <v>グループホーム吉祥</v>
       </c>
       <c r="E16" t="str">
-        <v>高松市木太町3749-3</v>
+        <v>高松市春日町1336-1</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -1105,19 +1105,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="str">
-        <v>34.33139778</v>
+        <v>34.32543444</v>
       </c>
       <c r="C17" t="str">
-        <v>134.09350611</v>
+        <v>134.08769306</v>
       </c>
       <c r="D17" t="str">
-        <v>グループホーム吉祥</v>
+        <v>グループホーム  春日</v>
       </c>
       <c r="E17" t="str">
-        <v>高松市春日町1336-1</v>
+        <v>高松市春日町671-1</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -1149,19 +1149,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="str">
-        <v>34.32543444</v>
+        <v>34.32825389</v>
       </c>
       <c r="C18" t="str">
-        <v>134.08769306</v>
+        <v>134.09985583</v>
       </c>
       <c r="D18" t="str">
-        <v>グループホーム  春日</v>
+        <v>グループホーム真珠の湯</v>
       </c>
       <c r="E18" t="str">
-        <v>高松市春日町671-1</v>
+        <v>高松市新田町甲2712-1</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -1193,19 +1193,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="str">
-        <v>34.32825389</v>
+        <v>34.31631917</v>
       </c>
       <c r="C19" t="str">
-        <v>134.09985583</v>
+        <v>134.10206972</v>
       </c>
       <c r="D19" t="str">
-        <v>グループホーム真珠の湯</v>
+        <v>グループホーム　ミモザ</v>
       </c>
       <c r="E19" t="str">
-        <v>高松市新田町甲2712-1</v>
+        <v>高松市新田町甲2181-1</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="str">
-        <v>34.31631917</v>
+        <v>34.34113889</v>
       </c>
       <c r="C20" t="str">
-        <v>134.10206972</v>
+        <v>134.11879528</v>
       </c>
       <c r="D20" t="str">
-        <v>グループホーム　ミモザ</v>
+        <v>グループホーム　エーデルワイス</v>
       </c>
       <c r="E20" t="str">
-        <v>高松市新田町甲2181-1</v>
+        <v>高松市高松町2160-1</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -1281,19 +1281,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="str">
-        <v>34.34113889</v>
+        <v>34.33625889</v>
       </c>
       <c r="C21" t="str">
-        <v>134.11879528</v>
+        <v>134.11294889</v>
       </c>
       <c r="D21" t="str">
-        <v>グループホーム　エーデルワイス</v>
+        <v>ニチイケアセンター古高松</v>
       </c>
       <c r="E21" t="str">
-        <v>高松市高松町2160-1</v>
+        <v>高松市高松町1718-2</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -1325,19 +1325,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="str">
-        <v>34.33625889</v>
+        <v>34.28601333</v>
       </c>
       <c r="C22" t="str">
-        <v>134.11294889</v>
+        <v>134.05931889</v>
       </c>
       <c r="D22" t="str">
-        <v>ニチイケアセンター古高松</v>
+        <v>認知症高齢者グループホーム第三若葉荘</v>
       </c>
       <c r="E22" t="str">
-        <v>高松市高松町1718-2</v>
+        <v>高松市上林町822-1</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1369,19 +1369,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="str">
-        <v>34.28601333</v>
+        <v>34.2964575</v>
       </c>
       <c r="C23" t="str">
-        <v>134.05931889</v>
+        <v>134.09948167</v>
       </c>
       <c r="D23" t="str">
-        <v>認知症高齢者グループホーム第三若葉荘</v>
+        <v>グループホーム邑</v>
       </c>
       <c r="E23" t="str">
-        <v>高松市上林町822-1</v>
+        <v>高松市前田西町1080-18</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -1413,19 +1413,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="str">
-        <v>34.2964575</v>
+        <v>34.25982833</v>
       </c>
       <c r="C24" t="str">
-        <v>134.09948167</v>
+        <v>134.10604083</v>
       </c>
       <c r="D24" t="str">
-        <v>グループホーム邑</v>
+        <v>グループホーム　らく楽十川</v>
       </c>
       <c r="E24" t="str">
-        <v>高松市前田西町1080-18</v>
+        <v>高松市十川東町938-1</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -1457,19 +1457,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="str">
-        <v>34.25982833</v>
+        <v>34.27957861</v>
       </c>
       <c r="C25" t="str">
-        <v>134.10604083</v>
+        <v>134.08590861</v>
       </c>
       <c r="D25" t="str">
-        <v>グループホーム　らく楽十川</v>
+        <v>グループホーム　うちんく</v>
       </c>
       <c r="E25" t="str">
-        <v>高松市十川東町938-1</v>
+        <v>高松市川島本町276-1</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -1501,19 +1501,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="str">
-        <v>34.27957861</v>
+        <v>34.28301083</v>
       </c>
       <c r="C26" t="str">
-        <v>134.08590861</v>
+        <v>134.06016611</v>
       </c>
       <c r="D26" t="str">
-        <v>グループホーム　うちんく</v>
+        <v>認知症高齢者グループホーム第五若葉荘</v>
       </c>
       <c r="E26" t="str">
-        <v>高松市川島本町276-1</v>
+        <v>高松市三谷町1643-1</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -1545,19 +1545,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="str">
-        <v>34.28301083</v>
+        <v>34.26881528</v>
       </c>
       <c r="C27" t="str">
-        <v>134.06016611</v>
+        <v>134.06000833</v>
       </c>
       <c r="D27" t="str">
-        <v>認知症高齢者グループホーム第五若葉荘</v>
+        <v>認知症高齢者グループホーム第六若葉荘</v>
       </c>
       <c r="E27" t="str">
-        <v>高松市三谷町1643-1</v>
+        <v>高松市三谷町4551-6</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -1589,19 +1589,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" t="str">
-        <v>34.26881528</v>
+        <v>34.28093889</v>
       </c>
       <c r="C28" t="str">
-        <v>134.06000833</v>
+        <v>134.06097722</v>
       </c>
       <c r="D28" t="str">
-        <v>認知症高齢者グループホーム第六若葉荘</v>
+        <v>認知症高齢者グループホーム若葉荘</v>
       </c>
       <c r="E28" t="str">
-        <v>高松市三谷町4551-6</v>
+        <v>高松市三谷町1654-5</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -1633,19 +1633,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" t="str">
-        <v>34.28093889</v>
+        <v>34.28840722</v>
       </c>
       <c r="C29" t="str">
-        <v>134.06097722</v>
+        <v>134.05028639</v>
       </c>
       <c r="D29" t="str">
-        <v>認知症高齢者グループホーム若葉荘</v>
+        <v>グループホーム　そよの里</v>
       </c>
       <c r="E29" t="str">
-        <v>高松市三谷町1654-5</v>
+        <v>高松市多肥上町504-2</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -1677,19 +1677,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" t="str">
-        <v>34.28840722</v>
+        <v>34.33550917</v>
       </c>
       <c r="C30" t="str">
-        <v>134.05028639</v>
+        <v>133.99654528</v>
       </c>
       <c r="D30" t="str">
-        <v>グループホーム　そよの里</v>
+        <v>グループホーム  きらら</v>
       </c>
       <c r="E30" t="str">
-        <v>高松市多肥上町504-2</v>
+        <v>高松市香西南町37-2</v>
       </c>
       <c r="F30" t="str">
         <v/>
@@ -1721,19 +1721,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="str">
-        <v>34.33550917</v>
+        <v>34.32829056</v>
       </c>
       <c r="C31" t="str">
-        <v>133.99654528</v>
+        <v>133.99665667</v>
       </c>
       <c r="D31" t="str">
-        <v>グループホーム  きらら</v>
+        <v>グループホーム  ひまわり</v>
       </c>
       <c r="E31" t="str">
-        <v>高松市香西南町37-2</v>
+        <v>高松市鬼無町藤井126-1</v>
       </c>
       <c r="F31" t="str">
         <v/>
@@ -1765,19 +1765,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" t="str">
-        <v>34.32829056</v>
+        <v>34.31449194</v>
       </c>
       <c r="C32" t="str">
-        <v>133.99665667</v>
+        <v>133.9959125</v>
       </c>
       <c r="D32" t="str">
-        <v>グループホーム  ひまわり</v>
+        <v>グループホーム菜の花</v>
       </c>
       <c r="E32" t="str">
-        <v>高松市鬼無町藤井126-1</v>
+        <v>高松市飯田町104-1</v>
       </c>
       <c r="F32" t="str">
         <v/>
@@ -1809,19 +1809,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" t="str">
-        <v>34.31449194</v>
+        <v>34.32354944</v>
       </c>
       <c r="C33" t="str">
-        <v>133.9959125</v>
+        <v>134.00077028</v>
       </c>
       <c r="D33" t="str">
-        <v>グループホーム菜の花</v>
+        <v>悠久の里　高松西</v>
       </c>
       <c r="E33" t="str">
-        <v>高松市飯田町104-1</v>
+        <v>高松市飯田町1334-4</v>
       </c>
       <c r="F33" t="str">
         <v/>
@@ -1853,19 +1853,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" t="str">
-        <v>34.32354944</v>
+        <v>34.24929111</v>
       </c>
       <c r="C34" t="str">
-        <v>134.00077028</v>
+        <v>133.99278167</v>
       </c>
       <c r="D34" t="str">
-        <v>悠久の里　高松西</v>
+        <v>グループホーム　悠悠香南</v>
       </c>
       <c r="E34" t="str">
-        <v>高松市飯田町1334-4</v>
+        <v>高松市香南町西庄182-1</v>
       </c>
       <c r="F34" t="str">
         <v/>
@@ -1897,19 +1897,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" t="str">
-        <v>34.24929111</v>
+        <v>34.24460806</v>
       </c>
       <c r="C35" t="str">
-        <v>133.99278167</v>
+        <v>133.98967361</v>
       </c>
       <c r="D35" t="str">
-        <v>グループホーム　悠悠香南</v>
+        <v>グループホーム　悠悠せんねん村</v>
       </c>
       <c r="E35" t="str">
-        <v>高松市香南町西庄182-1</v>
+        <v>高松市香南町西庄695-1</v>
       </c>
       <c r="F35" t="str">
         <v/>
@@ -1941,19 +1941,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" t="str">
-        <v>34.24460806</v>
+        <v>34.17937056</v>
       </c>
       <c r="C36" t="str">
-        <v>133.98967361</v>
+        <v>134.08689778</v>
       </c>
       <c r="D36" t="str">
-        <v>グループホーム　悠悠せんねん村</v>
+        <v>グループホーム　悠悠不動の滝</v>
       </c>
       <c r="E36" t="str">
-        <v>高松市香南町西庄695-1</v>
+        <v>高松市塩江町安原上東203-6</v>
       </c>
       <c r="F36" t="str">
         <v/>
@@ -1985,19 +1985,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" t="str">
-        <v>34.17937056</v>
+        <v>34.26443722</v>
       </c>
       <c r="C37" t="str">
-        <v>134.08689778</v>
+        <v>134.02720028</v>
       </c>
       <c r="D37" t="str">
-        <v>グループホーム　悠悠不動の滝</v>
+        <v>ひまわりの家</v>
       </c>
       <c r="E37" t="str">
-        <v>高松市塩江町安原上東203-6</v>
+        <v>高松市香川町大野901-1</v>
       </c>
       <c r="F37" t="str">
         <v/>
@@ -2029,19 +2029,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" t="str">
-        <v>34.26443722</v>
+        <v>34.24249278</v>
       </c>
       <c r="C38" t="str">
-        <v>134.02720028</v>
+        <v>134.03030917</v>
       </c>
       <c r="D38" t="str">
-        <v>ひまわりの家</v>
+        <v>グループホーム　ほととぎす</v>
       </c>
       <c r="E38" t="str">
-        <v>高松市香川町大野901-1</v>
+        <v>高松市香川町川東下672-5</v>
       </c>
       <c r="F38" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" t="str">
-        <v>34.24249278</v>
+        <v>34.3304825</v>
       </c>
       <c r="C39" t="str">
-        <v>134.03030917</v>
+        <v>134.15104</v>
       </c>
       <c r="D39" t="str">
-        <v>グループホーム　ほととぎす</v>
+        <v>高齢者グループホームプレスマン</v>
       </c>
       <c r="E39" t="str">
-        <v>高松市香川町川東下672-5</v>
+        <v>高松市牟礼町原932-1</v>
       </c>
       <c r="F39" t="str">
         <v/>
@@ -2117,19 +2117,19 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" t="str">
-        <v>34.3304825</v>
+        <v>34.29202444</v>
       </c>
       <c r="C40" t="str">
-        <v>134.15104</v>
+        <v>133.95774722</v>
       </c>
       <c r="D40" t="str">
-        <v>高齢者グループホームプレスマン</v>
+        <v>グループホームあいむ</v>
       </c>
       <c r="E40" t="str">
-        <v>高松市牟礼町原932-1</v>
+        <v>高松市国分寺町新名478-1</v>
       </c>
       <c r="F40" t="str">
         <v/>
@@ -2161,19 +2161,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" t="str">
-        <v>34.29202444</v>
+        <v>34.293583</v>
       </c>
       <c r="C41" t="str">
-        <v>133.95774722</v>
+        <v>133.996948</v>
       </c>
       <c r="D41" t="str">
-        <v>グループホームあいむ</v>
+        <v>グループホーム語り愛</v>
       </c>
       <c r="E41" t="str">
-        <v>高松市国分寺町新名478-1</v>
+        <v>高松市円座町字道下288-1</v>
       </c>
       <c r="F41" t="str">
         <v/>
@@ -2205,19 +2205,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" t="str">
-        <v>34.293583</v>
+        <v>34.288677</v>
       </c>
       <c r="C42" t="str">
-        <v>133.996948</v>
+        <v>134.003803</v>
       </c>
       <c r="D42" t="str">
-        <v>グループホーム語り愛</v>
+        <v>ネムの木　グループホーム　円座</v>
       </c>
       <c r="E42" t="str">
-        <v>高松市円座町字道下288-1</v>
+        <v>香川県高松市円座町94-1</v>
       </c>
       <c r="F42" t="str">
         <v/>
@@ -2249,19 +2249,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" t="str">
-        <v>34.288677</v>
+        <v>34.3239</v>
       </c>
       <c r="C43" t="str">
-        <v>134.003803</v>
+        <v>134.108288</v>
       </c>
       <c r="D43" t="str">
-        <v>ネムの木　グループホーム　円座</v>
+        <v>グループホーム　らく楽新田</v>
       </c>
       <c r="E43" t="str">
-        <v>香川県高松市円座町94-1</v>
+        <v>高松市新田町甲1144-3</v>
       </c>
       <c r="F43" t="str">
         <v/>
@@ -2293,19 +2293,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" t="str">
-        <v>34.3239</v>
+        <v>34.377899</v>
       </c>
       <c r="C44" t="str">
-        <v>134.108288</v>
+        <v>134.139091</v>
       </c>
       <c r="D44" t="str">
-        <v>グループホーム　らく楽新田</v>
+        <v>グループホーム　悠悠庵治の太陽</v>
       </c>
       <c r="E44" t="str">
-        <v>高松市新田町甲1144-3</v>
+        <v>高松市庵治町3822-１</v>
       </c>
       <c r="F44" t="str">
         <v/>
@@ -2337,19 +2337,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" t="str">
-        <v>34.377899</v>
+        <v>34.342305</v>
       </c>
       <c r="C45" t="str">
-        <v>134.139091</v>
+        <v>134.069126</v>
       </c>
       <c r="D45" t="str">
-        <v>グループホーム　悠悠庵治の太陽</v>
+        <v>グループホーム　リーラの家さくら</v>
       </c>
       <c r="E45" t="str">
-        <v>高松市庵治町3822-１</v>
+        <v>高松市福岡町四丁目12-18</v>
       </c>
       <c r="F45" t="str">
         <v/>
@@ -2381,19 +2381,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" t="str">
-        <v>34.342305</v>
+        <v>34.350465</v>
       </c>
       <c r="C46" t="str">
-        <v>134.069126</v>
+        <v>134.09462</v>
       </c>
       <c r="D46" t="str">
-        <v>グループホーム　リーラの家さくら</v>
+        <v>リーラの家　やしま</v>
       </c>
       <c r="E46" t="str">
-        <v>高松市福岡町四丁目12-18</v>
+        <v>高松市屋島西町893-1</v>
       </c>
       <c r="F46" t="str">
         <v/>
@@ -2425,19 +2425,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B47" t="str">
-        <v>34.350465</v>
+        <v>34.345285887234</v>
       </c>
       <c r="C47" t="str">
-        <v>134.09462</v>
+        <v>134.0400804522808</v>
       </c>
       <c r="D47" t="str">
-        <v>リーラの家　やしま</v>
+        <v>グループホーム新番丁</v>
       </c>
       <c r="E47" t="str">
-        <v>高松市屋島西町893-1</v>
+        <v>高松市番町二丁目14-2</v>
       </c>
       <c r="F47" t="str">
         <v/>
@@ -2469,19 +2469,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B48" t="str">
-        <v>34.322026</v>
+        <v>34.34331422027985</v>
       </c>
       <c r="C48" t="str">
-        <v>134.003625</v>
+        <v>134.06037192666588</v>
       </c>
       <c r="D48" t="str">
-        <v>グループホーム　オアシスＫ</v>
+        <v>グループホーム花クッカ</v>
       </c>
       <c r="E48" t="str">
-        <v>高松市飯田町705</v>
+        <v>高松市松福町一丁目12-3</v>
       </c>
       <c r="F48" t="str">
         <v/>
@@ -2513,19 +2513,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B49" t="str">
-        <v>34.345285887234</v>
+        <v>34.31613769511954</v>
       </c>
       <c r="C49" t="str">
-        <v>134.0400804522808</v>
+        <v>134.10228897180178</v>
       </c>
       <c r="D49" t="str">
-        <v>グループホーム新番丁</v>
+        <v>グループホームアカシア</v>
       </c>
       <c r="E49" t="str">
-        <v>高松市番町二丁目14-2</v>
+        <v>高松市新田町甲2180-1</v>
       </c>
       <c r="F49" t="str">
         <v/>
@@ -2557,19 +2557,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B50" t="str">
-        <v>34.34331422027985</v>
+        <v>34.29832458520862</v>
       </c>
       <c r="C50" t="str">
-        <v>134.06037192666588</v>
+        <v>133.9598471880089</v>
       </c>
       <c r="D50" t="str">
-        <v>グループホーム花クッカ</v>
+        <v>グループホームアイムの杜</v>
       </c>
       <c r="E50" t="str">
-        <v>高松市松福町一丁目12-3</v>
+        <v>高松市国分寺町新居1339-3</v>
       </c>
       <c r="F50" t="str">
         <v/>
@@ -2596,100 +2596,12 @@
         <v/>
       </c>
       <c r="N50" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>34.31613769511954</v>
-      </c>
-      <c r="C51" t="str">
-        <v>134.10228897180178</v>
-      </c>
-      <c r="D51" t="str">
-        <v>グループホームアカシア</v>
-      </c>
-      <c r="E51" t="str">
-        <v>高松市新田町甲2180-1</v>
-      </c>
-      <c r="F51" t="str">
-        <v/>
-      </c>
-      <c r="G51" t="str">
-        <v/>
-      </c>
-      <c r="H51" t="str">
-        <v/>
-      </c>
-      <c r="I51" t="str">
-        <v>認知症対応型共同生活介護</v>
-      </c>
-      <c r="J51" t="str">
-        <v/>
-      </c>
-      <c r="K51" t="str">
-        <v/>
-      </c>
-      <c r="L51" t="str">
-        <v/>
-      </c>
-      <c r="M51" t="str">
-        <v/>
-      </c>
-      <c r="N51" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>34.29832458520862</v>
-      </c>
-      <c r="C52" t="str">
-        <v>133.9598471880089</v>
-      </c>
-      <c r="D52" t="str">
-        <v>グループホームアイムの杜</v>
-      </c>
-      <c r="E52" t="str">
-        <v>高松市国分寺町新居1339-3</v>
-      </c>
-      <c r="F52" t="str">
-        <v/>
-      </c>
-      <c r="G52" t="str">
-        <v/>
-      </c>
-      <c r="H52" t="str">
-        <v/>
-      </c>
-      <c r="I52" t="str">
-        <v>認知症対応型共同生活介護</v>
-      </c>
-      <c r="J52" t="str">
-        <v/>
-      </c>
-      <c r="K52" t="str">
-        <v/>
-      </c>
-      <c r="L52" t="str">
-        <v/>
-      </c>
-      <c r="M52" t="str">
-        <v/>
-      </c>
-      <c r="N52" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N50"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/group_home/data.xlsx
+++ b/data/group_home/data.xlsx
@@ -577,7 +577,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="str">
         <v>34.28434611</v>
@@ -621,7 +621,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="str">
         <v>34.26092639</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="str">
         <v>34.31523417</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="str">
         <v>34.31362611</v>
@@ -753,7 +753,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="str">
         <v>34.322645</v>
@@ -797,7 +797,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="str">
         <v>34.32076472</v>
@@ -841,7 +841,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="str">
         <v>34.30706611</v>
@@ -885,7 +885,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="str">
         <v>34.30438028</v>
@@ -929,7 +929,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="str">
         <v>34.30271583</v>
@@ -973,7 +973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="str">
         <v>34.29199222</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="str">
         <v>34.32359278</v>
@@ -1061,7 +1061,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="str">
         <v>34.33139778</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" t="str">
         <v>34.32543444</v>
@@ -1149,7 +1149,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="str">
         <v>34.32825389</v>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" t="str">
         <v>34.31631917</v>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="str">
         <v>34.34113889</v>
@@ -1281,7 +1281,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" t="str">
         <v>34.33625889</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" t="str">
         <v>34.28601333</v>
@@ -1369,7 +1369,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="str">
         <v>34.2964575</v>
@@ -1413,7 +1413,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="str">
         <v>34.25982833</v>
@@ -1457,7 +1457,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="str">
         <v>34.27957861</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="str">
         <v>34.28301083</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" t="str">
         <v>34.26881528</v>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" t="str">
         <v>34.28093889</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" t="str">
         <v>34.28840722</v>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" t="str">
         <v>34.33550917</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" t="str">
         <v>34.32829056</v>
@@ -1765,7 +1765,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" t="str">
         <v>34.31449194</v>
@@ -1809,7 +1809,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" t="str">
         <v>34.32354944</v>
@@ -1853,7 +1853,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" t="str">
         <v>34.24929111</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" t="str">
         <v>34.24460806</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" t="str">
         <v>34.17937056</v>
@@ -1985,7 +1985,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" t="str">
         <v>34.26443722</v>
@@ -2029,7 +2029,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" t="str">
         <v>34.24249278</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" t="str">
         <v>34.3304825</v>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" t="str">
         <v>34.29202444</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="str">
         <v>34.293583</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" t="str">
         <v>34.288677</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" t="str">
         <v>34.3239</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" t="str">
         <v>34.377899</v>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" t="str">
         <v>34.342305</v>
@@ -2381,7 +2381,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" t="str">
         <v>34.350465</v>
@@ -2425,7 +2425,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B47" t="str">
         <v>34.345285887234</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B48" t="str">
         <v>34.34331422027985</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B49" t="str">
         <v>34.31613769511954</v>
@@ -2557,7 +2557,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B50" t="str">
         <v>34.29832458520862</v>

--- a/data/group_home/data.xlsx
+++ b/data/group_home/data.xlsx
@@ -677,7 +677,7 @@
         <v>西春日グループホーム</v>
       </c>
       <c r="E7" t="str">
-        <v>高松市西春日町1511-1</v>
+        <v>高松市西春日町1510-1</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -806,7 +806,7 @@
         <v>134.05430722</v>
       </c>
       <c r="D10" t="str">
-        <v>グループホームすずらん</v>
+        <v>グループホームまじゅん高松</v>
       </c>
       <c r="E10" t="str">
         <v>高松市伏石町2008-5</v>
@@ -2129,7 +2129,7 @@
         <v>グループホームあいむ</v>
       </c>
       <c r="E40" t="str">
-        <v>高松市国分寺町新名478-1</v>
+        <v>高松市国分寺町新名482-1</v>
       </c>
       <c r="F40" t="str">
         <v/>
